--- a/packages-generated/GB Accounts Company 2027-03-31 (Mar27) Excel 2007/Vatreturns.xlsx
+++ b/packages-generated/GB Accounts Company 2027-03-31 (Mar27) Excel 2007/Vatreturns.xlsx
@@ -40,7 +40,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="3">VATQtr4!$A$1:$I$31</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">VATQtr5!$A$1:$I$31</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="126"/>
       <c r="G5" s="42">
-        <v>45838</v>
+        <v>46203</v>
       </c>
       <c r="H5" s="10"/>
       <c r="I5" s="13"/>
@@ -13932,7 +13932,7 @@
       </c>
       <c r="F5" s="126"/>
       <c r="G5" s="42">
-        <v>45930</v>
+        <v>46295</v>
       </c>
       <c r="H5" s="10"/>
       <c r="I5" s="13"/>
@@ -14498,7 +14498,7 @@
       </c>
       <c r="F5" s="126"/>
       <c r="G5" s="42">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="H5" s="10"/>
       <c r="I5" s="13"/>
@@ -15064,7 +15064,7 @@
       </c>
       <c r="F5" s="126"/>
       <c r="G5" s="42">
-        <v>46112</v>
+        <v>46477</v>
       </c>
       <c r="H5" s="10"/>
       <c r="I5" s="13"/>
@@ -15630,7 +15630,7 @@
       </c>
       <c r="F5" s="126"/>
       <c r="G5" s="42">
-        <v>46142</v>
+        <v>46507</v>
       </c>
       <c r="H5" s="10"/>
       <c r="I5" s="13"/>
